--- a/results/job_matches_2026-09-01.xlsx
+++ b/results/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G62"/>
+  <dimension ref="A1:G84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,17 +503,17 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer - Azure Databricks</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>AmeriHealth Caritas</t>
+          <t>Aramark</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Newtown Square, PA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -521,34 +521,34 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e6ebb2e53d9fa7b</t>
+          <t>https://www.indeed.com/viewjob?jk=39460deda6cc7046</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Cloud Vulnerability Management Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,7 +556,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Vertex AI, Scala, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,42 +566,42 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dbf686b10c85ee8a</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d72577f6e997de</t>
         </is>
       </c>
     </row>
@@ -713,17 +713,17 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>AI Engineer Intern</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Copart, Inc</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, PostgreSQL, MySQL, NoSQL, ETL, CI/CD, Jenkins</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=222ed3cc9231d113</t>
+          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, HBase, PostgreSQL, MySQL, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,24 +776,24 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
+          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Azure AI Platform Engineer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
@@ -801,34 +801,34 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
+          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Solutions Architect II (Epic)</t>
+          <t>Azure AI Platform Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
@@ -836,34 +836,34 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
+          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>BI / Data Architect (Remote)-4</t>
+          <t>Solutions Architect II (Epic)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Marlborough, MA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -871,7 +871,7 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, RDS, Azure, Databricks, Unity Catalog, Spark, Scala, Kafka, Snowflake</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,7 +881,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=63e9cfe1d5416339</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
         </is>
       </c>
     </row>
@@ -1133,17 +1133,17 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1151,7 +1151,7 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,14 +1161,14 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d7dae841c8ca70</t>
+          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,14 +1196,14 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd39fb0b7173c935</t>
+          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcabdc4b09803cb</t>
+          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-4</t>
+          <t>Data Engineer - SQL</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>R+L Carriers</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
+          <t>https://www.indeed.com/viewjob?jk=178200f6a03318c5</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5978dbd7180d8</t>
+          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect- Onsite- Richmond, VA</t>
+          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, Oracle, SQL Server, NoSQL, CI/CD, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19db03ed84045bd5</t>
+          <t>https://www.indeed.com/viewjob?jk=74d7dae841c8ca70</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Infrastructure Solutions Architect</t>
+          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64e2dee8091e6c26</t>
+          <t>https://www.indeed.com/viewjob?jk=cd39fb0b7173c935</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Azistinc.</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Danforth, IL, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d86ffea72e55e7</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcabdc4b09803cb</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Sr. Azure Databricks Data Engineer / Architect</t>
+          <t>Senior Data Engineer-4</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Mission, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Boston</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22baba519bae8200</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f5978dbd7180d8</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Data and AI Engineer II</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Azure, Spark, Snowflake, Data Modeling, dbt, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Software Engineer - CHG (Hybrid)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Burlington, VT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Azistinc.</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Danforth, IL, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,24 +1581,24 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4d86ffea72e55e7</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
+          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
+          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Sr. Azure Databricks Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Mission, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Federal Reserve Bank of Boston</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,7 +1711,7 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
+          <t>https://www.indeed.com/viewjob?jk=22baba519bae8200</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Vantage Point Logistics</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
+          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Decatur, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, Power BI, DataOps, MLOps</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,32 +1791,32 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,32 +1826,32 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f92d9adfa8ac131</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer, Web Development</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cimarron Trailers</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chickasha, OK, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,32 +1861,32 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cabf765c3ea3a52</t>
+          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AI-Centric Release &amp; Automation Software Engineer</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,32 +1931,32 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,32 +1966,32 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - February 2027</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Development Infrastructure</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
+          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Advisor II, Data Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,14 +2071,14 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Software Engineer III-Python/PySpark</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
@@ -2088,15 +2088,15 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Vantage Point Logistics</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Decatur, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, Power BI, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aacef118912fb72</t>
+          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d944de70b19936</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Wells Fargo</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e454f81b70c0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=8f92d9adfa8ac131</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Development Tester</t>
+          <t>Software Engineer, Web Development</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Cimarron Trailers</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chickasha, OK, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b097e917dd1a75c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3cabf765c3ea3a52</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Enterprise Integration Software Engineer</t>
+          <t>AI-Centric Release &amp; Automation Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Shamrock Foods Company</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Commerce City, CO, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
+          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Shamrock Foods Company</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
+          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Technology Development Program Associate - February 2027</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Oracle, SQL Server, PostgreSQL, ETL, Tableau, Tableau Server, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>AI Engineer</t>
+          <t>Sr. Software Engineer, Development Infrastructure</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Xactus</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Broomall, PA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, ETL, MLflow, CI/CD, Terraform, Docker, Kubernetes, AKS</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-06-22</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dec641935aaf0ea6</t>
+          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
+          <t>https://www.indeed.com/viewjob?jk=e2baf0a1ca3ae8cf</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>Ecentria</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,19 +2561,19 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Integrations - AI/ML</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Kafka, Kafka Connect, Data Modeling, dbt, Tableau, MLOps, Airflow</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,777 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1251b27601bc9eff</t>
+          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>Software Development Engineer - US Federal</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Workday</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>Reston, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E63" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E64" t="inlineStr">
+        <is>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+        </is>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>CapTech Consulting</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+        </is>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G65" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E66" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G66" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>Business Intelligence Architect</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>Diasorin</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E67" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G67" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>Cloud Infrastructure Architect</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>Infoorigin Inc</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>Richmond, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E68" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G68" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=7ca74489755db701</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>Java Application Architect</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E69" t="inlineStr">
+        <is>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G69" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E70" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G70" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4aacef118912fb72</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E71" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G71" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=19d944de70b19936</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E72" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G72" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39e454f81b70c0eb</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>Software Development Tester</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>Charles Schwab</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>Austin, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E73" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+        </is>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G73" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b097e917dd1a75c6</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E74" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G74" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E75" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G75" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E76" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G76" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>Specialist IS Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E77" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G77" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>Enterprise Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>Amway</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>Ada, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E78" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G78" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E79" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+        </is>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G79" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>Shamrock Foods Company</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>Commerce City, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E80" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+        </is>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G80" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Shamrock Foods Company</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E81" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+        </is>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G81" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E82" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Oracle, SQL Server, PostgreSQL, ETL, Tableau, Tableau Server, Git</t>
+        </is>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Drupal Developer – Senior</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>NuAxis Innovations</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, MySQL, CI/CD, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=de484ff1a65cd9c4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-01.xlsx
+++ b/results/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G84"/>
+  <dimension ref="A1:G95"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Banc of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,34 +696,34 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
+          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,24 +731,24 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
+          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -758,7 +758,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
@@ -766,147 +766,147 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, HBase, PostgreSQL, MySQL, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Azure AI Platform Engineer</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Solutions Architect II (Epic)</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
+          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Software Engineering – Senior Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Banc of California</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,67 +916,67 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
+          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineering, Sr Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Synopsys</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-06-25</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7c27d39498fc808</t>
+          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Mid-Level Java Developer</t>
+          <t>Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, HBase, PostgreSQL, MySQL, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd12e2b62f9cde</t>
+          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,67 +1021,67 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
+          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Azure AI Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
+          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Solutions Architect II (Epic)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,19 +1091,19 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Software Engineering – Senior Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -1112,11 +1112,11 @@
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aab1ba56e62f502</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Mid-Level Java Developer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Antra, Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Sterling, VA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
+          <t>https://www.indeed.com/viewjob?jk=37bd12e2b62f9cde</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Senior Engineer, ML Data Services</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
+          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Senior Engineer, ML Data Services</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
+          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer - SQL</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>R+L Carriers</t>
+          <t>Nexus One</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,19 +1266,19 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178200f6a03318c5</t>
+          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>clickhouse</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
+          <t>https://www.indeed.com/viewjob?jk=8aab1ba56e62f502</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Sr. Software Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>CDK Global</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d7dae841c8ca70</t>
+          <t>https://www.indeed.com/viewjob?jk=8504ecddbd720c65</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd39fb0b7173c935</t>
+          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcabdc4b09803cb</t>
+          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-4</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
+          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5978dbd7180d8</t>
+          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data and AI Engineer II</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Snowflake, Data Modeling, dbt, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
+          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Software Engineer - CHG (Hybrid)</t>
+          <t>Data Engineer - SQL</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>R+L Carriers</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Ocala, FL, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
+          <t>https://www.indeed.com/viewjob?jk=178200f6a03318c5</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Azistinc.</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Danforth, IL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4d86ffea72e55e7</t>
+          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
+          <t>https://www.indeed.com/viewjob?jk=74d7dae841c8ca70</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,14 +1651,14 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=cd39fb0b7173c935</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Sr. Azure Databricks Data Engineer / Architect</t>
+          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
@@ -1668,15 +1668,15 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Mission, CA, US USA</t>
+          <t>Pittsburgh, PA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>11.8</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=5fcabdc4b09803cb</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer-4</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Boston</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,102 +1721,102 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22baba519bae8200</t>
+          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
+          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Kafka Platform Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>American Electric Power</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Burlington, VT, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
@@ -1826,24 +1826,24 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=e8f5978dbd7180d8</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Data and AI Engineer II</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,7 +1851,7 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Spark, Snowflake, Data Modeling, dbt, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Software Engineer - CHG (Hybrid)</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,24 +1931,24 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
+          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Azure Databricks Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mission, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Federal Reserve Bank of Boston</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Scala, ETL, CI/CD, Terraform, Git</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
+          <t>https://www.indeed.com/viewjob?jk=22baba519bae8200</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Advisor II, Data Engineer</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
+          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer III-Python/PySpark</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
+          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Vantage Point Logistics</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Burlington, VT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
+          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Decatur, IL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, Power BI, DataOps, MLOps</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,67 +2176,67 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
+          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
+          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior Power BI &amp; GCP Data Analytics Consultant (contract)</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Wells Fargo</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Scala, Data Modeling, ETL, ELT, Power BI, Git</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8f92d9adfa8ac131</t>
+          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer, Web Development</t>
+          <t>Energy Data Scientist</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Cimarron Trailers</t>
+          <t>EnergyHub</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Chickasha, OK, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Scala, PostgreSQL, MySQL, Data Modeling, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,32 +2281,32 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3cabf765c3ea3a52</t>
+          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,32 +2316,32 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI-Centric Release &amp; Automation Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
+          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Site Reliability Engineer- REMOTE - Onsite Training</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>10.4</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb47baecd105cce</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
+          <t>Advisor II, Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - February 2027</t>
+          <t>Software Engineer III-Python/PySpark</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,32 +2456,32 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Development Infrastructure</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Vantage Point Logistics</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
+          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,32 +2491,32 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
+          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>ADM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Decatur, IL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, Power BI, DataOps, MLOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,102 +2526,102 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2baf0a1ca3ae8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Ecentria</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Architect Commerce Cloud (Hybris) -Mountain View, CA</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+          <t>https://www.indeed.com/viewjob?jk=9795ec11042c6f19</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>AI-Centric Release &amp; Automation Software Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
+          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Diasorin</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
+          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Architect</t>
+          <t>Technology Development Program Associate - February 2027</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca74489755db701</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Sr. Software Engineer, Development Infrastructure</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
+          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Youth Villages</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Chesterfield, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aacef118912fb72</t>
+          <t>https://www.indeed.com/viewjob?jk=e2baf0a1ca3ae8cf</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ecentria</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d944de70b19936</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e454f81b70c0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Tester</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, NoSQL, Splunk, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b097e917dd1a75c6</t>
+          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CapTech Consulting</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
+          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
+          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Specialist IS Business Systems Analyst</t>
+          <t>Solution Designer/Architect (SPM/ICM)</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Enterprise Integration Software Engineer</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>Diasorin</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+          <t>AWS, IAM, Azure, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca74489755db701</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shamrock Foods Company</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Commerce City, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
+          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Shamrock Foods Company</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
+          <t>https://www.indeed.com/viewjob?jk=4aacef118912fb72</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Analyst</t>
+          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Oracle, SQL Server, PostgreSQL, ETL, Tableau, Tableau Server, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+          <t>https://www.indeed.com/viewjob?jk=19d944de70b19936</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
+          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Pelico</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
+          <t>https://www.indeed.com/viewjob?jk=39e454f81b70c0eb</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Drupal Developer – Senior</t>
+          <t>Specialist IS Business Systems Analyst</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>NuAxis Innovations</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,15 +3356,400 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Enterprise Integration Software Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Amway</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>Ada, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>Grainger</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Data Scientist</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ellipsis Health</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>San Francisco, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>Shamrock Foods Company</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Commerce City, CO, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Shamrock Foods Company</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Phoenix, AZ, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Data Analyst</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Citizens</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Johnston, RI, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, RDS, Oracle, SQL Server, PostgreSQL, ETL, Tableau, Tableau Server, Git</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>VIE - Software Engineer (based in Miami)</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Pelico</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Infrastructure Engineer III</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>JPMorganChase</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Plano, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Site Reliability Engineer</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>nan</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5fae225772bb11f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Drupal Developer – Senior</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>NuAxis Innovations</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Washington, DC, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
           <t>AWS, S3, API Gateway, RDS, Scala, Kafka, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de484ff1a65cd9c4</t>
         </is>

--- a/results/job_matches_2026-09-01.xlsx
+++ b/results/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G95"/>
+  <dimension ref="A1:G87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -538,17 +538,17 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -556,147 +556,147 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
+          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Vulnerability Management Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d72577f6e997de</t>
+          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
+          <t>Backend Go Developer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Datasage Technologies</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9068d6b5e88e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=e37c3bd53b7199c8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dc3b9fad3404f3</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d72577f6e997de</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
+          <t>https://www.indeed.com/viewjob?jk=9127ac581bc7c947</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Senior Security Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,84 +741,84 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
+          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e9068d6b5e88e56b</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
+          <t>https://www.indeed.com/viewjob?jk=64dc3b9fad3404f3</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -836,7 +836,7 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,14 +846,14 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
+          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -863,7 +863,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
@@ -881,24 +881,24 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Banc of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,34 +906,34 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,24 +941,24 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,112 +976,112 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, HBase, PostgreSQL, MySQL, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
+          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Azure AI Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Banc of California</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
+          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Solutions Architect II (Epic)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,32 +1091,32 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
+          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Software Engineering – Senior Engineer</t>
+          <t>Site Reliability Engineer I</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, HBase, PostgreSQL, MySQL, Cassandra, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
@@ -1126,32 +1126,32 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
+          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Mid-Level Java Developer</t>
+          <t>Senior Cloud Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Antra, Inc</t>
+          <t>Worldpay</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Sterling, VA, US USA</t>
+          <t>Cincinnati, OH, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, PostgreSQL, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,67 +1161,67 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=37bd12e2b62f9cde</t>
+          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Azure AI Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-08-28</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
+          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Solutions Architect II (Epic)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>Quest Diagnostics</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Secaucus, NJ, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>13.2</v>
+        <v>14.6</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,32 +1231,32 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
+          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Software Engineering – Senior Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Senior Engineer, ML Data Services</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>clickhouse</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,7 +1291,7 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,24 +1301,24 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8aab1ba56e62f502</t>
+          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer</t>
+          <t>Senior Engineer, ML Data Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CDK Global</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8504ecddbd720c65</t>
+          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nexus One</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,7 +1361,7 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
+          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,34 +1396,34 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Consulting SWE</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
+          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
+          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
+          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer - SQL</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>R+L Carriers</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Ocala, FL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Data Lake Storage, Scala, Dimensional Modeling, Star Schema, Fact Tables, Dimension Tables</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=178200f6a03318c5</t>
+          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,7 +1571,7 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,14 +1581,14 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
+          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=74d7dae841c8ca70</t>
+          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cd39fb0b7173c935</t>
+          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Java Full Stack Developer (Angular/Kafka)</t>
+          <t>Senior Data Engineer-4</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Pittsburgh, PA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fcabdc4b09803cb</t>
+          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-4</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Cloud Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=3b46c450dd05f14e</t>
         </is>
       </c>
     </row>
@@ -2008,17 +2008,17 @@
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Federal Reserve Bank of Boston</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Scala, ETL, CI/CD, Terraform, Git</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,24 +2036,24 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22baba519bae8200</t>
+          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Cloud-Native Architect</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
+          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
+          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
         </is>
       </c>
     </row>
@@ -2323,17 +2323,17 @@
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Site Reliability Engineer- REMOTE - Onsite Training</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Memphis, TN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
+          <t>https://www.indeed.com/viewjob?jk=fbb47baecd105cce</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- REMOTE - Onsite Training</t>
+          <t>Advisor II, Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb47baecd105cce</t>
+          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Advisor II, Data Engineer</t>
+          <t>Software Engineer III-Python/PySpark</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,7 +2411,7 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,24 +2421,24 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
+          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Software Engineer III-Python/PySpark</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vantage Point Logistics</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Westerville, OH, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
+          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Architect Commerce Cloud (Hybris) -Mountain View, CA</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Vantage Point Logistics</t>
+          <t>Photon</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,34 +2481,34 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
+          <t>https://www.indeed.com/viewjob?jk=9795ec11042c6f19</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ADM</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Decatur, IL, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, ETL, Power BI, DataOps, MLOps</t>
+          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9189c721d2bd01c6</t>
+          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>AI-Centric Release &amp; Automation Software Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
+          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Architect Commerce Cloud (Hybris) -Mountain View, CA</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9795ec11042c6f19</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>AI-Centric Release &amp; Automation Software Engineer</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Technology Development Program Associate - February 2027</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
+          <t>Sr. Software Engineer, Development Infrastructure</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>LinkedIn</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - February 2027</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Ecentria</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Development Infrastructure</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
+          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Youth Villages</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Chesterfield, VA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, SQL Server, MySQL, ETL, ELT, Tableau, Git</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2baf0a1ca3ae8cf</t>
+          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ecentria</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Cloud &amp; AI/AL Architect</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Flash Inspector</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Solution Designer/Architect (SPM/ICM)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Diasorin</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,19 +3016,19 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
+          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Engineering Associate Consultant (Graduating Dec 2026 - Summer 2027)</t>
+          <t>Cloud Infrastructure Architect</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>CapTech Consulting</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Redshift, S3, RDS, Azure, Data Factory, Blob Storage, Google Cloud Platform, SQL Server</t>
+          <t>AWS, IAM, Azure, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ad9985af3e772076</t>
+          <t>https://www.indeed.com/viewjob?jk=7ca74489755db701</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Solution Designer/Architect (SPM/ICM)</t>
+          <t>Specialist IS Business Systems Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Amgen</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Thousand Oaks, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Diasorin</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
+          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Architect</t>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Shamrock Foods Company</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Commerce City, CO, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca74489755db701</t>
+          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Shamrock Foods Company</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
+          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4aacef118912fb72</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ellipsis Health</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19d944de70b19936</t>
+          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Full Stack Developer (Java, Spring Boot &amp; Angular)</t>
+          <t>Enterprise Integration Software Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Amway</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Ada, MI, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39e454f81b70c0eb</t>
+          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Specialist IS Business Systems Analyst</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=5fae225772bb11f0</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Enterprise Integration Software Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Amway</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Ada, MI, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+          <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Drupal Developer – Senior</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>NuAxis Innovations</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, MySQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3470,286 +3470,6 @@
         </is>
       </c>
       <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Shamrock Foods Company</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>Commerce City, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Shamrock Foods Company</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Phoenix, AZ, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Senior Data Analyst</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Citizens</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>Johnston, RI, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, RDS, Oracle, SQL Server, PostgreSQL, ETL, Tableau, Tableau Server, Git</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=788a20ff7253f53b</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>VIE - Software Engineer (based in Miami)</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Pelico</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, MongoDB, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d71007f33dca61fb</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fae225772bb11f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Drupal Developer – Senior</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>NuAxis Innovations</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, MySQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=de484ff1a65cd9c4</t>
         </is>

--- a/results/job_matches_2026-09-01.xlsx
+++ b/results/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G87"/>
+  <dimension ref="A1:G82"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -503,60 +503,60 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Aramark</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>19.4</v>
+        <v>18.8</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, GCP, BigQuery, Scala, Snowflake, ETL, ELT</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39460deda6cc7046</t>
+          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Managing Consultant, Databricks Engineer - Dallas</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,67 +566,67 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Cloud Vulnerability Management Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, IAM, RDS, Azure, Databricks, Hadoop, Spark, Scala, Kafka</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c5c68f432e3b3384</t>
+          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Backend Go Developer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Datasage Technologies</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>17.4</v>
+        <v>18.8</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e37c3bd53b7199c8</t>
+          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MFour Mobile Research, Inc.</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Kansas City, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>16.7</v>
+        <v>18.1</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,32 +671,32 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7d72577f6e997de</t>
+          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Backend Go Developer</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>REPAY</t>
+          <t>Datasage Technologies</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,24 +706,24 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9127ac581bc7c947</t>
+          <t>https://www.indeed.com/viewjob?jk=e37c3bd53b7199c8</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Security Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>DoorDash</t>
+          <t>MFour Mobile Research, Inc.</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Kansas City, MO, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
@@ -731,7 +731,7 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka</t>
+          <t>AWS, Kinesis, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, PostgreSQL</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,102 +741,102 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
+          <t>https://www.indeed.com/viewjob?jk=b7d72577f6e997de</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
+          <t>Data Engineer, Data and Insights</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>United Jewish Appeal-Fed of Jewish</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Spark, PySpark, Scala, SQL Server, PostgreSQL, MySQL, ETL</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9068d6b5e88e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=1faa4e13a3b0f326</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>REPAY</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, RDS, Databricks, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dc3b9fad3404f3</t>
+          <t>https://www.indeed.com/viewjob?jk=9127ac581bc7c947</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Senior Security Data Engineer</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>DoorDash</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>15.3</v>
+        <v>16.7</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Kinesis, Redshift, IAM, RDS, GCP, BigQuery, Dataflow, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,84 +846,84 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
+          <t>https://www.indeed.com/viewjob?jk=b31c422fadc318ca</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
+          <t>https://www.indeed.com/viewjob?jk=e9068d6b5e88e56b</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
+          <t>Sr Software Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>American Express</t>
+          <t>Ameriprise Financial</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
+          <t>https://www.indeed.com/viewjob?jk=64dc3b9fad3404f3</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Campus Undergraduate Full-Time Analyst - 2027 Data Engineer I, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -933,7 +933,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,7 +941,7 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,14 +951,14 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
+          <t>https://www.indeed.com/viewjob?jk=9f92c9f4c62df8b2</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,14 +986,14 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
+          <t>https://www.indeed.com/viewjob?jk=21c4624adc67b18e</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,24 +1021,24 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
+          <t>https://www.indeed.com/viewjob?jk=615c775c5cae3f87</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Charlotte, NC</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Banc of California</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Scala, Snowflake, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
+          <t>https://www.indeed.com/viewjob?jk=4a1f26919bbd5f4b</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Campus Undergraduate Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,24 +1081,24 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, BigQuery, Hive, HBase, Scala, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
+          <t>https://www.indeed.com/viewjob?jk=5f6abea4f1a0a28b</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer I</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Phoenix, AZ</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Sunrise, FL, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,112 +1116,112 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, HBase, PostgreSQL, MySQL, Cassandra, NoSQL, Splunk</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=af69fed96c27a33f</t>
+          <t>https://www.indeed.com/viewjob?jk=e7c88978b19e1fac</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Senior Cloud Engineer</t>
+          <t>Campus Graduate Masters Summer Internship Program - 2027 Data Engineer, Enterprise Technology Services- Sunrise, FL</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Worldpay</t>
+          <t>American Express</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Cincinnati, OH, US USA</t>
+          <t>Sunrise, FL, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, IAM, RDS, Hive, Spark, Scala</t>
+          <t>AWS, RDS, BigQuery, Hive, HBase, Scala, Oracle, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a1afe8b7a5cf447e</t>
+          <t>https://www.indeed.com/viewjob?jk=24d421e34cea4cb0</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Azure AI Platform Engineer</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Banc of California</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, NoSQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Data Lake Storage, Medallion Architecture, Scala, Snowflake, dbt</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-08-28</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=58f19beac4a8df7f</t>
+          <t>https://www.indeed.com/viewjob?jk=29ffdd693ba7b433</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Solutions Architect II (Epic)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Quest Diagnostics</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Secaucus, NJ, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Athena, RDS, Azure, Databricks, GCP, Scala, Snowflake, PostgreSQL</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,19 +1231,19 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1fcda0d42014a823</t>
+          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Software Engineering – Senior Engineer</t>
+          <t>Forward deployed engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1252,46 +1252,46 @@
         </is>
       </c>
       <c r="D24" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Software Engineering – Senior Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
+          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
+          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
+          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,24 +1406,24 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
+          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Consulting SWE</t>
+          <t>Senior Engineer, ML Data Services</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1431,34 +1431,34 @@
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
+          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Senior Engineer, ML Data Services</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Motional</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,7 +1466,7 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,24 +1476,24 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
+          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Senior Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Nexus One</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,34 +1536,34 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Consulting SWE</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
+          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
+          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=133fdba617ad39ad</t>
+          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer-4</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Spark, PySpark, Scala, Snowflake, Oracle, SQL Server, dbt, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,102 +1686,102 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fe15a8ff19071aee</t>
+          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Solutions Architect</t>
+          <t>Sr. Java FSD - Hybrid</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Lake Mary, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b46c450dd05f14e</t>
+          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>DevOps Engineer + HPC</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,24 +1791,24 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
+          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Kafka Platform Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>American Electric Power</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,139 +1816,139 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Scala, Kafka, Kafka Connect, Oracle, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8f5978dbd7180d8</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4d347d17e2c8a</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data and AI Engineer II</t>
+          <t>Cloud Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Snowflake, Data Modeling, dbt, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
+          <t>https://www.indeed.com/viewjob?jk=3b46c450dd05f14e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Software Engineer - CHG (Hybrid)</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
+          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Data and AI Engineer II</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Freeport-McMoRan</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Azure, Spark, Snowflake, Data Modeling, dbt, DataOps, MLOps, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Sr. Azure Databricks Data Engineer / Architect</t>
+          <t>Software Engineer - CHG (Hybrid)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Mission, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,24 +2001,24 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2026,7 +2026,7 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,14 +2036,14 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
+          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Cloud-Native Architect</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
@@ -2061,7 +2061,7 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Terraform</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,24 +2071,24 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3bba1497145f4051</t>
+          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Azure Databricks Data Engineer / Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Mission, CA, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,7 +2096,7 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,24 +2106,24 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
+          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Veeva Vault Consultant</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Burlington, VT, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ea4dcf33b2c6a0fa</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0cb7879bc668d4</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41548be738a76cc8</t>
+          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8103a63d2d3d1da7</t>
+          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,112 +2246,112 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=13f4312108b4db79</t>
+          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Energy Data Scientist</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>EnergyHub</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Scala, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26603fc5c3af6f4d</t>
+          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer- REMOTE - Onsite Training</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Memphis, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>HBase, NoSQL, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbb47baecd105cce</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
         </is>
       </c>
     </row>
@@ -2393,17 +2393,17 @@
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Engineer III-Python/PySpark</t>
+          <t>Sr Data Engineering Architect – Fraud Domain</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, ETL, CI/CD, Airflow</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcb46275b507c630</t>
+          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Architect, Browser Extension Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Vantage Point Logistics</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Westerville, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,17 +2446,17 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Snowflake, SQL Server, PostgreSQL, Dimensional Modeling, ETL, ELT, dbt, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a30d8a15dec2e27</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
         </is>
       </c>
     </row>
@@ -2603,17 +2603,17 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Senior Software Engineer - PA053</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,34 +2621,34 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Senior Software Engineer - PA051</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - February 2027</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Software Engineer, Development Infrastructure</t>
+          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>LinkedIn</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Spark, Scala, Kafka, MySQL, MongoDB, Cassandra, NoSQL, Git</t>
+          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fde89f0085f48d4</t>
+          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Technology Development Program Associate - February 2027</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Ecentria</t>
+          <t>Capital One</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Senior Platform &amp; SRE Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Cupertino, CA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Platform DevOps Engineer - Senior Associate (Enterprise Data Solutions)</t>
+          <t>Senior Dev Ops Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Ecentria</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Northbrook, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Scala, Kafka, CI/CD, Jenkins, Jenkins, Git, Python</t>
+          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7088241af78eed3</t>
+          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI/AL Architect</t>
+          <t>AI Platform Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Flash Inspector</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Solution Designer/Architect (SPM/ICM)</t>
+          <t>Software Development Engineer - US Federal</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,19 +2981,19 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Cloud &amp; AI/AL Architect</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Diasorin</t>
+          <t>Flash Inspector</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -3006,34 +3006,34 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
+          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Architect</t>
+          <t>Solution Designer/Architect (SPM/ICM)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Irving, TX, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Oracle, SQL Server, NoSQL, Azure DevOps, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7ca74489755db701</t>
+          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Business Intelligence Architect</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Diasorin</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eac8dc0954e3729c</t>
+          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
+          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+          <t>Senior Software Developer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Shamrock Foods Company</t>
+          <t>Prodapt Solutions</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Commerce City, CO, US USA</t>
+          <t>Portland, OR, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4fe730220968ca4b</t>
+          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer (PL/SQL &amp; TSQL)</t>
+          <t>Site Reliability Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Shamrock Foods Company</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, Oracle, SQL Server, Data Modeling, ETL, SQL</t>
+          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33309cfbf855421f</t>
+          <t>https://www.indeed.com/viewjob?jk=5fae225772bb11f0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Infrastructure Engineer III</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Ellipsis Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, MLOps, Python, Scala, R</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,182 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=39ec559199e3af57</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Enterprise Integration Software Engineer</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Amway</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>Ada, MI, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, GCP, Cloud Storage, Scala, Kafka, CI/CD, Docker, Airflow, Apache Airflow</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b546afd28257f1d7</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Site Reliability Engineer</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5fae225772bb11f0</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Infrastructure Engineer III</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Plano, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Drupal Developer – Senior</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>NuAxis Innovations</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, S3, API Gateway, RDS, Scala, Kafka, MySQL, CI/CD, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-08-31</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=de484ff1a65cd9c4</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-09-01.xlsx
+++ b/results/job_matches_2026-09-01.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G82"/>
+  <dimension ref="A1:G97"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,42 +468,42 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Royal Caribbean Group</t>
+          <t>Thought Logic Consulting</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Miramar, FL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, IAM, RDS, Azure, Databricks, GCP, BigQuery, HBase</t>
+          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=15bc705887f3d3f9</t>
+          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Atlanta</t>
+          <t>Managing Consultant, Databricks Engineer - Dallas</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -513,7 +513,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
@@ -531,14 +531,14 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=592db50bf0a7db56</t>
+          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Dallas</t>
+          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -548,7 +548,7 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
@@ -566,24 +566,24 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fdd852c33d90d087</t>
+          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Managing Consultant, Databricks Engineer - Minneapolis</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Thought Logic Consulting</t>
+          <t>DailyPay Inc</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Minneapolis, MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
@@ -591,7 +591,7 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, Databricks, Unity Catalog, Delta Live Tables, BigQuery, Spark, PySpark, Scala</t>
+          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=344f4e1ed7c40432</t>
+          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Data Solutions Architect</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>DailyPay Inc</t>
+          <t>Smart Tech Skills LLC</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, ECS, IAM, Azure, Blob Storage, GCP, Vertex AI</t>
+          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,32 +636,32 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=059d00b010e64ab8</t>
+          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Data Solutions Architect</t>
+          <t>Pharma Data Engineer – Databricks AWS</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Smart Tech Skills LLC</t>
+          <t>RadCube</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Spark</t>
+          <t>AWS, Glue, Athena, S3, ECS, RDS, Azure, Databricks, Unity Catalog, GCP</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
@@ -671,7 +671,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=501460a7402af538</t>
+          <t>https://www.indeed.com/viewjob?jk=79c01255fde37758</t>
         </is>
       </c>
     </row>
@@ -853,12 +853,12 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Technology Consultant - Cloud &amp; Full Stack Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -871,34 +871,34 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, RDS, Azure, Spark, Scala, Splunk, CI/CD</t>
+          <t>AWS, Glue, EMR, S3, RDS, Azure, Data Factory, Databricks, Hadoop, Spark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e9068d6b5e88e56b</t>
+          <t>https://www.indeed.com/viewjob?jk=f72936d7adf83912</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Sr Software Engineer</t>
+          <t>CE Data Architect</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Ameriprise Financial</t>
+          <t>Eli Lilly</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Indianapolis, IN, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,17 +906,17 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, S3, API Gateway, ECS, IAM, RDS, Hive, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, Spark, PySpark, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=64dc3b9fad3404f3</t>
+          <t>https://www.indeed.com/viewjob?jk=d68553dbf5364e11</t>
         </is>
       </c>
     </row>
@@ -1203,17 +1203,17 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Databricks Architect</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Vynca</t>
+          <t>Confiz</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>San Mateo, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,42 +1221,42 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
+          <t>AWS, IAM, RDS, Azure, Databricks, Unity Catalog, Medallion Architecture, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b5450e0d89b0a1</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Forward deployed engineer</t>
+          <t>Backend Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Fellow</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
+          <t>AWS, Lambda, S3, SQS, API Gateway, ECS, IAM, Scala, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
+          <t>https://www.indeed.com/viewjob?jk=3c077d0d8d52c113</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Software Engineering – Senior Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>FICO</t>
+          <t>Vynca</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>13.9</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, SQS, RDS, Scala, Kafka, SQL Server, PostgreSQL, MySQL, MongoDB, DynamoDB</t>
+          <t>AWS, Kinesis, Redshift, RDS, BigQuery, Spark, Scala, Spark Streaming, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ff95b66842bb690</t>
+          <t>https://www.indeed.com/viewjob?jk=1d41697c1443e407</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer-Healthcare Analytics (Full-Time)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>MRCOOL, LLC</t>
+          <t>The Iowa Clinic</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Hickory, KY, US USA</t>
+          <t>West Des Moines, IA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Redshift, RDS, Azure, GCP, BigQuery, Spark, Scala, Kafka, Snowflake</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,67 +1336,67 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
+          <t>https://www.indeed.com/viewjob?jk=444da39c1f86bc7a</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, S3, RDS, Azure, Databricks, GCP, BigQuery, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-05-06</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
+          <t>https://www.indeed.com/viewjob?jk=2834f9c283bafcc9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Forward deployed engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Incident IQ</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, Cassandra, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,137 +1406,137 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
+          <t>https://www.indeed.com/viewjob?jk=e8c67c9d37ef5af9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>General Motors (GM)</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, Medallion Architecture, GCP, Spark, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=10208da6da41d304</t>
+          <t>https://www.indeed.com/viewjob?jk=5c63b933c1725f3d</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Engineer, ML Data Services</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Motional</t>
+          <t>MRCOOL, LLC</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Hickory, KY, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, Step Functions, S3, API Gateway, RDS, Spark, Scala, DynamoDB</t>
+          <t>RDS, Data Lake Storage, Google Cloud Platform, BigQuery, Dataflow, Cloud Storage, Scala, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=473eb45015763f16</t>
+          <t>https://www.indeed.com/viewjob?jk=4b45327f8bc50c30</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Nexus One</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, RDS, Azure, GCP, YARN, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=73fcaa363d33fefe</t>
+          <t>https://www.indeed.com/viewjob?jk=9a94b3adee01a833</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Pacific Gas and Electric</t>
+          <t>Incident IQ</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Oakland, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
+          <t>AWS, Redshift, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server, PostgreSQL, MongoDB</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
+          <t>https://www.indeed.com/viewjob?jk=bccca4539903f22e</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Consulting SWE</t>
+          <t>GCP Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>J2B GLOBAL LLC</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Columbus, IN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
+          <t>Databricks, Google Cloud Platform, GCP, BigQuery, Dataflow, Spark, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,94 +1581,94 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
+          <t>https://www.indeed.com/viewjob?jk=794b8cc5a876cb0f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Palo Alto, CA, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, EMR, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
+          <t>https://www.indeed.com/viewjob?jk=c0ef720fc915d5a7</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, EMR, Lambda, Athena, S3, API Gateway, ECS, IAM, RDS, PostgreSQL</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
+          <t>https://www.indeed.com/viewjob?jk=7b089978304c281b</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
+          <t>Data Platform Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>GEICO</t>
+          <t>Pacific Gas and Electric</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Oakland, CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,34 +1676,34 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
+          <t>AWS, Lambda, Redshift, S3, RDS, Azure, Data Lake Storage, Blob Storage, Cloud Storage, Scala</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
+          <t>https://www.indeed.com/viewjob?jk=2c7c0ea011bc1581</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Consulting SWE</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,34 +1711,34 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>Azure, Event Hubs, Scala, Kafka, PostgreSQL, MySQL, NoSQL, Data Modeling, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=477a93dc9faf4820</t>
+          <t>https://www.indeed.com/viewjob?jk=0b372b96d1263fff</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Sr. Java FSD - Hybrid</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Lake Mary, FL, US USA</t>
+          <t>Palo Alto, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1746,7 +1746,7 @@
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ceeac6f66e099ea</t>
+          <t>https://www.indeed.com/viewjob?jk=43f2ff091a75531a</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>DevOps Engineer + HPC</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>EL SHADDAI TECHNOLOGIES</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,77 +1781,77 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
+          <t>https://www.indeed.com/viewjob?jk=1dde48c17b527b0d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Machine Learning Engineer II, Document &amp; Vision Intelligence</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Infoorigin Inc</t>
+          <t>GEICO</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, MLOps</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eba4d347d17e2c8a</t>
+          <t>https://www.indeed.com/viewjob?jk=341131fbbffbdd46</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Cloud Infrastructure Solutions Architect</t>
+          <t>DevOps Engineer + HPC</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>EL SHADDAI TECHNOLOGIES</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
+          <t>AWS, Azure, Google Cloud Platform, Scala, SQL Server, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
@@ -1861,24 +1861,24 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3b46c450dd05f14e</t>
+          <t>https://www.indeed.com/viewjob?jk=637e4cf76137493c</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Pioneering Evolution</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, VA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,7 +1886,7 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>Azure, Event Hubs, Kafka, PostgreSQL, Azure Cosmos DB, Data Modeling, ETL, ELT, REST API integration, CI/CD</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,24 +1896,24 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8cc53575e5fa190b</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Business Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Ness Digital Engineering</t>
+          <t>Buyers Edge Platform</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minneapolis, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,7 +1921,7 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
+          <t>AWS, Redshift, RDS, Databricks, Snowflake, SQL Server, Data Modeling, ETL, ELT, Airflow</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,207 +1931,207 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
+          <t>https://www.indeed.com/viewjob?jk=1bb53d18980f0f7f</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data and AI Engineer II</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Freeport-McMoRan</t>
+          <t>Cognizant</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Naperville, IL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Azure, Spark, Snowflake, Data Modeling, dbt, DataOps, MLOps, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f3bb3edbb44ae52d</t>
+          <t>https://www.indeed.com/viewjob?jk=f8c3f1635bd7570e</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Software Engineer - CHG (Hybrid)</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Infoorigin Inc</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
+          <t>https://www.indeed.com/viewjob?jk=eba4d347d17e2c8a</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer III</t>
+          <t>Cloud Infrastructure Solutions Architect</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Richmond, VA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, SQL Server, NoSQL, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
+          <t>https://www.indeed.com/viewjob?jk=3b46c450dd05f14e</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>OCI Cloud Engineer</t>
+          <t>Software Engineer III (Full Stack Engineer)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, Kafka, PostgreSQL, DynamoDB, Cassandra</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
+          <t>https://www.indeed.com/viewjob?jk=c984a40e303625f4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Sr. Azure Databricks Data Engineer / Architect</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Cognizant</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Mission, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, Data Modeling, CI/CD</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e2979cdcefff4b84</t>
+          <t>https://www.indeed.com/viewjob?jk=ef3f1d7e3dce5d5b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Veeva Vault Consultant</t>
+          <t>Business Analyst</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Ness Digital Engineering</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>North Brunswick, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
+          <t>Kinesis, Redshift, RDS, Databricks, BigQuery, Scala, Kafka, Snowflake, NoSQL, Data Modeling</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bb0cb7879bc668d4</t>
+          <t>https://www.indeed.com/viewjob?jk=26924b3ed57d2d37</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Java</t>
+          <t>Sr Software Engineer (B2B Scores)</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>FICO</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,34 +2166,34 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, Scala, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
+          <t>https://www.indeed.com/viewjob?jk=e7a1053e369bbe3b</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>GRP Solutions</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Dayton, OH, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, NoSQL, Splunk, CI/CD, Jenkins, Maven, Terraform</t>
+          <t>AWS, EMR, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9e67dd75dd6fb51d</t>
+          <t>https://www.indeed.com/viewjob?jk=0aba217de8f47ca1</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Software Engineer - CHG (Hybrid)</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>ServiceTitan</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, SQS, SNS, ECS, Scala, Kafka, PostgreSQL, DynamoDB, NoSQL</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,102 +2246,102 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
+          <t>https://www.indeed.com/viewjob?jk=e1c855c396d5779f</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Site Reliability Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
+          <t>https://www.indeed.com/viewjob?jk=d112005b7fa18a95</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>OCI Cloud Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, IAM, RDS, Hive, Oracle, MySQL, CI/CD, Jenkins, GitHub Actions, Terraform</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
+          <t>https://www.indeed.com/viewjob?jk=168bc86279b2f3a1</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior SecDevOps Engineer</t>
+          <t>Veeva Vault Consultant</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Re:Build Manufacturing</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>North Brunswick, NJ, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Data Modeling, ETL, ELT, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
+          <t>https://www.indeed.com/viewjob?jk=bb0cb7879bc668d4</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Advisor II, Data Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Phillips 66</t>
+          <t>ServiceTitan</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
+          <t>AWS, Lambda, Redshift, RDS, Azure, Scala, Kafka, Snowflake, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,54 +2386,54 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
+          <t>https://www.indeed.com/viewjob?jk=00dce8c243c5b7df</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Sr Data Engineering Architect – Fraud Domain</t>
+          <t>Senior Software Engineer - Java</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Realign</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Cleveland, OH, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Azure, Scala, Kafka, Oracle, SQL Server, PostgreSQL, CI/CD</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
+          <t>https://www.indeed.com/viewjob?jk=b86346652daa564d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Architect, Browser Extension Platform</t>
+          <t>Epic Ambulatory Analyst</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Keeper Security, Inc.</t>
+          <t>Vnsure Business Solution</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -2442,11 +2442,11 @@
         </is>
       </c>
       <c r="D58" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Oracle, SQL Server, PostgreSQL, MySQL, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
+          <t>https://www.indeed.com/viewjob?jk=10fe83e92cc26811</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Architect Commerce Cloud (Hybris) -Mountain View, CA</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Photon</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9795ec11042c6f19</t>
+          <t>https://www.indeed.com/viewjob?jk=49b77b548d132ade</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Equifax</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
+          <t>https://www.indeed.com/viewjob?jk=fa41aecb1be7e339</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>AI-Centric Release &amp; Automation Software Engineer</t>
+          <t>Senior SecDevOps Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>General Motors (GM)</t>
+          <t>Re:Build Manufacturing</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Sunnyvale, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,34 +2551,34 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, ETL, ELT, Power BI, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f342fde2939be0a1</t>
+          <t>https://www.indeed.com/viewjob?jk=f6cff7b7ecdf07ee</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>SR SOFTWARE ENGINEER</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Dollar General</t>
+          <t>DocuSign</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Goodlettsville, TN, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
+          <t>Azure, Blob Storage, GCP, Cloud Storage, Scala, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-27</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
+          <t>https://www.indeed.com/viewjob?jk=eccb85ffecfc1db0</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA053</t>
+          <t>Onsite_GCP Cloud Engineer _Sunnyvale, CA</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>THEMESOFT</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Sunnyvale, CA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>IAM, RDS, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,32 +2631,32 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
+          <t>https://www.indeed.com/viewjob?jk=60889a2a51a50e18</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - PA051</t>
+          <t>Sr. Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Sunbelt Rentals</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Bethesda, MD, US USA</t>
+          <t>Fort Mill, SC, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Databricks, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
+          <t>https://www.indeed.com/viewjob?jk=7bfea736a070f184</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Advisor II, Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>State Farm</t>
+          <t>Phillips 66</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>RDS, Azure, Databricks, Unity Catalog, Scala, ETL, ELT, CI/CD, Azure DevOps, Python</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,137 +2701,137 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
+          <t>https://www.indeed.com/viewjob?jk=79a66f24c8a4ff20</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
+          <t>Senior Java Developer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Information Technology Senior Management Forum</t>
+          <t>Shrive Technologies LLC</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Bloomington, IL, US USA</t>
+          <t>Rahway, NJ, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
+          <t>AWS, Azure, Scala, Kafka, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
+          <t>https://www.indeed.com/viewjob?jk=548ef62de9391d04</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer Full Stack / Backend I (Full Time) - United States</t>
+          <t>Principle SRE</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Merative</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, NoSQL, CI/CD, Terraform, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Kafka, NoSQL, CI/CD, Terraform, Kubernetes, AKS, Azure Monitor</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc603f90a12b6ae5</t>
+          <t>https://www.indeed.com/viewjob?jk=e4c859aac5cb3cfd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Technology Development Program Associate - February 2027</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Capital One</t>
+          <t>SiloSmashers</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, NoSQL, Jenkins, Terraform, Docker, Kubernetes, Jenkins, Python</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef7c81c1f347080d</t>
+          <t>https://www.indeed.com/viewjob?jk=bebd8ca219c8abde</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; SRE Engineer</t>
+          <t>Sr Data Engineering Architect – Fraud Domain</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Realign</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Cleveland, OH, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>RDS, Databricks, Spark, PySpark, Scala, Kafka, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,137 +2841,137 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+          <t>https://www.indeed.com/viewjob?jk=ec55e22c79aa31d8</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+          <t>Senior Software Architect, Browser Extension Platform</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Keeper Security, Inc.</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Cupertino, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+          <t>AWS, Lambda, IAM, RDS, Databricks, Scala, Data Modeling, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+          <t>https://www.indeed.com/viewjob?jk=ee2a9223c60a8a70</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Dev Ops Engineer</t>
+          <t>Software Dev/Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Ecentria</t>
+          <t>GROWMARK</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Northbrook, IL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Glue, Lambda, Athena, S3, API Gateway, ECS, RDS, SQL Server, CodeBuild</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a5845354c696ba9</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>AI Platform Engineer</t>
+          <t>Software Architecture - Sr Advisor I</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Fiserv</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jacksonville, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Kafka Connect, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+          <t>https://www.indeed.com/viewjob?jk=56e2bc0bf1616b18</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Development Engineer - US Federal</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Equifax</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Alpharetta, GA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Splunk, CI/CD, Jenkins, Terraform, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, GCP, Cassandra, Splunk, CI/CD, Jenkins, Maven, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,94 +2981,94 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ee75da69e5cdf2fa</t>
+          <t>https://www.indeed.com/viewjob?jk=257b8fbaa0833fbe</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Cloud &amp; AI/AL Architect</t>
+          <t>SR SOFTWARE ENGINEER</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Flash Inspector</t>
+          <t>Dollar General</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Goodlettsville, TN, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
+          <t>S3, Azure, GCP, Scala, Kafka, Oracle, PostgreSQL, Cassandra, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-09-01</t>
+          <t>2026-07-27</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+          <t>https://www.indeed.com/viewjob?jk=9b9dc28bec37638a</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Solution Designer/Architect (SPM/ICM)</t>
+          <t>Software Engineer, Identity and Access Management</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Fitch Group</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
+          <t>AWS, Lambda, API Gateway, IAM, Oracle, PostgreSQL, MongoDB, DynamoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
+          <t>https://www.indeed.com/viewjob?jk=4316a6d89bd9dfac</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Business Intelligence Architect</t>
+          <t>Senior Software Engineer - PA053</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Diasorin</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,34 +3076,34 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, Snowflake, Data Modeling, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c67304245b883992</t>
+          <t>https://www.indeed.com/viewjob?jk=571921f25acb7de3</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Specialist IS Business Systems Analyst</t>
+          <t>Senior Software Engineer - PA051</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Amgen</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Thousand Oaks, CA, US USA</t>
+          <t>Bethesda, MD, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+          <t>AWS, Azure, GCP, Scala, Kafka, MongoDB, NoSQL, CI/CD, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+          <t>https://www.indeed.com/viewjob?jk=c9cfb23165ea9cf6</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>State Farm</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Databricks, Spark, PySpark, Scala, Snowflake, CI/CD, GitHub Actions, Git</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ac749b1ab9e374</t>
+          <t>https://www.indeed.com/viewjob?jk=d276a1bbc3a5d721</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Developer</t>
+          <t>Mid-Level DATA ENGINEER: Microsoft Power Platform &amp; AI Copilot Studio (HYBRID)</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Prodapt Solutions</t>
+          <t>Information Technology Senior Management Forum</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Portland, OR, US USA</t>
+          <t>Bloomington, IL, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Scala, Snowflake, Data Modeling, Power BI, DataOps</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
+          <t>https://www.indeed.com/viewjob?jk=75d140e1ecf0b230</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Site Reliability Engineer</t>
+          <t>Senior Agentic Data Engineer (IC3)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>ClassLink, Inc.</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,34 +3216,34 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, PostgreSQL, CI/CD, GitHub Actions, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Scala, Snowflake, PostgreSQL, ETL, ELT, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5fae225772bb11f0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f5a95e8fe9cae63</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,34 +3251,34 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-01</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8b8836b6912f122e</t>
+          <t>https://www.indeed.com/viewjob?jk=47380ec921538261</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Infrastructure Engineer III</t>
+          <t>Data Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,17 +3286,542 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Splunk, CI/CD, Terraform, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Terraform, Docker, Kubernetes, Airflow, Git</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
         <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G82" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6adbeed2597d8049</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>Data Engineer - Compensation Systems</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E83" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Data Factory, Databricks, Blob Storage, Medallion Architecture, Oracle, SQL Server, Data Modeling, ELT</t>
+        </is>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G83" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=d50bd21e18b27caf</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>Data Engineer</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>Sunbelt Rentals</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>Fort Mill, SC, US USA</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E84" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Databricks, Blob Storage, Event Hubs, Unity Catalog, Medallion Architecture, Delta Live Tables, Spark, Kafka</t>
+        </is>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G84" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0ee3cca78dd562a5</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>Senior Platform &amp; SRE Engineer</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E85" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G85" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=8020034c387753ba</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>Data Engineer - Data Platform (Spark/Kafka/Flink/Scala/Java)</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>NTT DATA</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>Cupertino, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E86" t="inlineStr">
+        <is>
+          <t>Azure, Spark, Scala, Kafka, PostgreSQL, Cassandra, CI/CD, Kubernetes, Airflow, Apache Airflow</t>
+        </is>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
           <t>2026-08-31</t>
         </is>
       </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bd4ac402c96b6348</t>
+      <c r="G86" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5052a528569a1695</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>Senior Dev Ops Engineer</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>Ecentria</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>Northbrook, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E87" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, MySQL, Cassandra, Terraform, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G87" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5a8f7629eee2b42e</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>AI Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>BV Teck</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>Remote, US USA</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E88" t="inlineStr">
+        <is>
+          <t>AWS, API Gateway, Azure, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Terraform, Docker</t>
+        </is>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G88" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=75649a2a273f051e</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>Senior Full Stack Developer – Java &amp; Spring Boot and Angular</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>Cognizant</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>Lake Mary, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E89" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, NoSQL, CI/CD, Docker</t>
+        </is>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=156dda493f603ad2</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>Jersey City, NJ, US USA</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E90" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b313a1b84f660028</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>Tampa, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G91" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3cb1cfad2ce1fa38</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>Senior Java Developer</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>Luxoft</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E92" t="inlineStr">
+        <is>
+          <t>RDS, Scala, Kafka, Oracle, NoSQL, Data Modeling, Kubernetes, SonarQube, Git, Bitbucket</t>
+        </is>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G92" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5af3bc833528c5f0</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>Cloud &amp; AI/AL Architect</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>Flash Inspector</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>Atlanta, GA, US USA</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E93" t="inlineStr">
+        <is>
+          <t>IAM, RDS, Google Cloud Platform, GCP, Scala, MLOps, CI/CD, Git, Python, SQL</t>
+        </is>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-09-01</t>
+        </is>
+      </c>
+      <c r="G93" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=880c4f664a765490</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>Solution Designer/Architect (SPM/ICM)</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>Irving, TX, US USA</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E94" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, Oracle, ETL, ELT, Power BI</t>
+        </is>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G94" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=4ef4ef7d1e24d2a4</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>Senior Engineer – Apply For CircleCard</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>Target</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>Brooklyn Park, MN, US USA</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E95" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD, Docker, Kubernetes, Python</t>
+        </is>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G95" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=9dc57cd1efbc6ee0</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>Specialist IS Business Systems Analyst</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>Amgen</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>Thousand Oaks, CA, US USA</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E96" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, ETL, Power BI, Tableau, CI/CD, AKS</t>
+        </is>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G96" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=c6db11c42ce1f3de</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>Senior Software Developer</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>Prodapt Solutions</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>Portland, OR, US USA</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E97" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, CI/CD, Jenkins, Azure DevOps, Maven, Docker, Kubernetes, AKS</t>
+        </is>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-08-31</t>
+        </is>
+      </c>
+      <c r="G97" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=e49334a6de85ce3c</t>
         </is>
       </c>
     </row>
